--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,12 +608,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Remote - US • Remote</t>
+          <t>Senior AWS Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,28 +622,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AWS Consultant</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
+          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Messaging Systems Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Platforms and Automation</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60174baa1f0aad14</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ce4ef971ec1d26</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=30ce4ef971ec1d26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Test Automation Engineer - Regrello</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b704bbe9b05b2c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Varsity Spirit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Longview, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e407fb3775f7a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business System Analyst II</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96dc7676fb3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Full Stack | AI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3260,76 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Full Stack | AI Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Net Health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf9fe4c0bcd7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b22cbf19f8a0047</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Application Developer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf9fe4c0bcd7c6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
+          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AWS Consultant</t>
+          <t>Big Data Application Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
+          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior AWS Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71a9aca92494410</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Cloud Systems Administrator</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Five Rivers IT, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
+          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd35c029ba02435f</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Solutions Architect</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=a71a9aca92494410</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Sr. Cloud Systems Administrator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Five Rivers IT, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd35c029ba02435f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>GCP Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,77 +1361,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, API Gateway, RDS, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcb623acf634f6d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ce4ef971ec1d26</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>Messaging Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,11 +2267,11 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Varsity Spirit</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Longview, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack | AI Developer</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,260 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CCaaS GCP Product Owner</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Betsol</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AI Software Engineer Intern- Bastazo</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Technical Architect - Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Avid Technology</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst I - REMOTE</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Net Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>GCP Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Solutions Architect</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,29 +1291,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, RDS, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcb623acf634f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Messaging Systems Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,29 +3181,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,15 +3496,155 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Software Engineer Intern- Bastazo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Technical Architect - Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Avid Technology</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst I - REMOTE</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Net Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,172 +1301,172 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,662 +1476,662 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,417 +2316,417 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,277 +2771,277 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3072,11 +3072,11 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,119 +3086,119 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,40 +3611,1755 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Fieldwire</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer - Azure</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Messaging Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Esri</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Redlands, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Aperia</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nestlé Purina</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Regrello</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cayuse Holdings</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Early Warning Services</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Business Intelligence Data Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CONNEXUS CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Varsity Spirit</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>LINEVISION</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Biztec Global</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Automation Engineer - Senior</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EvergreenHealth</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Engineer - Business Analytics</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Primoris Services Corporation</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>iClassPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Longview, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer - Finance Technology Solutions</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Coding</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Coding</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Handshake</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Omada Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior DevOps/MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Leverege</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Vacatia, Inc.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Azure Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>iHealth Innovative Solutions</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Coreforce</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ThesisGrid</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Red Hat OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Snowflake Architect</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Biztec Global</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Vytalize Health</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Cloudera/hadoop specialist.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CCaaS GCP Product Owner</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Betsol</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Software Engineer Intern- Bastazo</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Technical Architect - Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Avid Technology</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Net Health</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D141" t="n">
         <v>10.4</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3268,25 +3268,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Messaging Systems Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Software Engineer II - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,69 +3951,69 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>Varsity Spirit</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Longview, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
         </is>
       </c>
     </row>
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Avid Technology</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5325,41 +5325,6 @@
         </is>
       </c>
       <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Net Health</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Cloud Systems Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Five Rivers IT, Inc.</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - C# / Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,209 +1151,209 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd35c029ba02435f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Cloud Systems Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Five Rivers IT, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GCP Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,164 +3016,164 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,19 +3226,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,137 +3261,137 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,59 +3436,59 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Messaging Systems Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Sr. Solutions Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Disney Parks, Experiences and Products</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,77 +3951,77 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Snowflake, SQL Server, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafc948111731821</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5be813c11826da</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,129 +4066,129 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Software Engineer II - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Learn Beyond Consulting</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=75af597329b51c24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,102 +4381,102 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Varsity Spirit</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Longview, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,67 +4871,67 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,59 +4976,59 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,29 +5036,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Analyst, Audible People &amp; Places</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>Audible</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Data Modeling, ETL, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=761fd113897ed8f1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Business System Analyst II</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,7 +5326,182 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9527921e8a58fef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI Software Engineer Intern- Bastazo</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Technical Architect - Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Avid Technology</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,52 +993,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71a9aca92494410</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a71a9aca92494410</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Cloud Systems Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Five Rivers IT, Inc.</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Solutions Architect</t>
+          <t>Sr. Cloud Systems Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Five Rivers IT, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Senior Power BI Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Essent Guaranty, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GCP Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Platform Engineer – Robotics &amp; AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lens Technology Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, S3, Databricks, BigQuery, Cloud Storage, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=605d83d5c08b6a96</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,172 +3191,172 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Baer Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,217 +3461,217 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Disney Parks, Experiences and Products</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Snowflake, SQL Server, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5be813c11826da</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Messaging Systems Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Sr. Solutions Analyst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Disney Parks, Experiences and Products</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Snowflake, SQL Server, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5be813c11826da</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,102 +4241,102 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Learn Beyond Consulting</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75af597329b51c24</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,94 +4346,94 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Software Engineer II - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Learn Beyond Consulting</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=75af597329b51c24</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,102 +4626,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>iClassPro, Inc.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Longview, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,137 +5046,137 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Analyst, Audible People &amp; Places</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Audible</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Data Modeling, ETL, Amazon QuickSight, Power BI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761fd113897ed8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Business System Analyst II</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9527921e8a58fef3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. System Administrator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Analyst, Audible People &amp; Places</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>Audible</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,17 +5491,227 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Data Modeling, ETL, Amazon QuickSight, Power BI</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=761fd113897ed8f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Business System Analyst II</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma, Inc.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9527921e8a58fef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI Software Engineer Intern- Bastazo</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Technical Architect - Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Arista Networks</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Avid Technology</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Devops – Azure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>DISTILLERY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Hive, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
+          <t>https://www.indeed.com/viewjob?jk=eb316c4d0d8d4a0b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
+          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AWS Consultant</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
+          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Senior AWS Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer – Robotics &amp; AI</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lens Technology Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, BigQuery, Cloud Storage, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605d83d5c08b6a96</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
+          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,24 +3671,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Baer Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,69 +3741,69 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Solutions Analyst</t>
+          <t>Data Platform Engineer – Microsoft Fabric</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Disney Parks, Experiences and Products</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Snowflake, SQL Server, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5be813c11826da</t>
+          <t>https://www.indeed.com/viewjob?jk=58d5075d31f14eb7</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,24 +4336,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Software Engineer II - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,15 +4398,15 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
@@ -4598,17 +4598,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
@@ -4668,25 +4668,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,102 +4696,102 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Longview, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf4ebf8be88af31</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,54 +5186,54 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5242,38 +5242,38 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Sr. System Administrator</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. System Administrator</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Analyst, Audible People &amp; Places</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Audible</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Data Modeling, ETL, Amazon QuickSight, Power BI</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,217 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761fd113897ed8f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Business System Analyst II</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Williams-Sonoma, Inc.</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9527921e8a58fef3</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Technical Architect - Enterprise Data</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Arista Networks</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Warehouse Architect</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Avid Technology</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fe7381654ca4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53b79d933c22cf0c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf9fe4c0bcd7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Big Data Application Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Big Data Application Developer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devops – Azure</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DISTILLERY</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Hadoop, Hive, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb316c4d0d8d4a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
+          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Senior AWS Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AWS Consultant</t>
+          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
+          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71a9aca92494410</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Systems Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Five Rivers IT, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Power BI Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Essent Guaranty, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Cloud Systems Administrator</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Five Rivers IT, Inc.</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Architect</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Essent Guaranty, Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Solutions Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Menasha, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,182 +3426,182 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,102 +3716,102 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097e08533f03ba37</t>
+          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb930b934fbc187</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The Baer Group</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Microtek Learning</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Silver Spring, MD, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,102 +3891,102 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Messaging Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd2ae0ade6192a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,172 +4136,172 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Platform Engineer – Microsoft Fabric</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d5075d31f14eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,172 +4311,172 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30419cda8d1db5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II - Full Stack Engineer</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4a46b9a6c0e288</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,49 +4486,49 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Learn Beyond Consulting</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75af597329b51c24</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4538,50 +4538,50 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,102 +4626,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. System Administrator</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,19 +4836,19 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,637 +4871,112 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e841fc413765b399</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Software Engineering, Sr Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Synopsys</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Santa Fe, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>JSSA</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>IT Data Scientist</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>AdventHealth Corporate</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Altamonte Springs, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Azure Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>iHealth Innovative Solutions</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Coreforce</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Grafana Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Red Hat OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Sr. System Administrator</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Stellar Solutions</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Cloudera/hadoop specialist.</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Technical Architect - Enterprise Data</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Arista Networks</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9e10d0ccdb5375</t>
+          <t>https://www.indeed.com/viewjob?jk=1b22cbf19f8a0047</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b22cbf19f8a0047</t>
+          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Big Data Application Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01844276a565bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Big Data Application Developer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
+          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Senior AWS Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Consultant</t>
+          <t>Cloud Infrastructure Engineer – AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
+          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Architect SME – Cloud-Native Platforms &amp; Data Systems</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175460c5974ef2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Systems Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Five Rivers IT, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Cloud Systems Administrator</t>
+          <t>Senior Power BI Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Five Rivers IT, Inc.</t>
+          <t>Essent Guaranty, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
+          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Essent Guaranty, Inc.</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Baer Group</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Engineer, Software Engineer - Angular and Java</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,129 +3786,129 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,19 +3961,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Universal City, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,42 +4091,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,49 +4486,49 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4538,15 +4538,15 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,67 +4591,67 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Workday Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, Docker, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937091ef92a9caaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=e841fc413765b399</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Sr. System Administrator</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Cloudera/hadoop specialist.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. System Administrator</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4835,146 +4835,6 @@
         </is>
       </c>
       <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Enterprise Knowledge</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e841fc413765b399</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,42 +3506,42 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. QA Automation Engineer - Brokerage / Financial Services Domain (FTE / Hybrid)</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62912356a020a29b</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
+          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,42 +3776,42 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,94 +3821,94 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Engineering</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Universal City, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,94 +4171,94 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Universal City, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Vacatia, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,67 +4486,67 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,67 +4556,67 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Workday Engineer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e841fc413765b399</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. System Administrator</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,59 +4696,59 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5a50150ef4b66b</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,402 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Grafana Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Grafana Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Red Hat OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Workday Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>College Board</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Java Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Softpath System LLC</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sr. System Administrator</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Stellar Solutions</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Cloudera/hadoop specialist.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Dynamo Technologies</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI Software Engineer Intern- Bastazo</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Winterville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, Step Functions, RDS, Kafka, Tableau, Tableau Server, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=653b8eca70818820</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,52 +3321,52 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=062dd989576d1fde</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Baer Group</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
@@ -3863,35 +3863,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Universal City, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,42 +4196,42 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Universal City, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=3338bda845b857ff</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4516,29 +4516,29 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf986da2977e0aa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Workday Engineer</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>College Board</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Enterprise Knowledge</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
+          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. System Administrator</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,19 +5081,19 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cloudera/hadoop specialist.</t>
+          <t>Senior Workday Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Hadoop, HDFS, Hive, Oozie, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c169f4920a033c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Sr. System Administrator</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Winterville, NC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,15 +5211,50 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Winterville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Redshift, Step Functions, RDS, Kafka, Tableau, Tableau Server, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=653b8eca70818820</t>
         </is>

--- a/results/job_matches_2026-07-16.xlsx
+++ b/results/job_matches_2026-07-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Application Developer</t>
+          <t>Software Engineer - iOS/Android</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0eb18b3d5109ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7bf7c8fec07038</t>
+          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004a662bac9f5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7aaa1ab54a6fb47</t>
+          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer - iOS/Android</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Excel Sports Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdde81364ace6b88</t>
+          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS Consultant</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bcb64699ea21836</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422dd8e9c739fe77</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Excel Sports Management</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, SQS, Azure, GCP, PostgreSQL</t>
+          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c48dbd46696795</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Vertex AI, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3a80ab86734aea</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba9a5d942e523c5</t>
+          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Hadoop/Spark/OCP/Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa14baaf9fd7957</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeade119569bbf7</t>
+          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93edda5c98f4cdb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1cdcb324b377bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bc1107dcef567b</t>
+          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Power BI Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>Essent Guaranty, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfab6ea52221dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1bb8e723d49656</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Cloud Systems Administrator</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Five Rivers IT, Inc.</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc684f1ebf7d965</t>
+          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111eb98b6df0e036</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Architect</t>
+          <t>Azure Data Engineer – AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Essent Guaranty, Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b04eecb0db1a644</t>
+          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c7b5c770c1535f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf29b9a8949927c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e9ac43a4c79de0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data Engineer – AI &amp; Data Platform</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ea6d5281a59460</t>
+          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6f565a0cba9b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93a6382b79298c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c55cbc7a32077d</t>
+          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfd9be8468f66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f547f3d8df9f9bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54854fd47b363a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45df0d1609c8367b</t>
+          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bdc76018751755</t>
+          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43290df41714a389</t>
+          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b16b2331ee1aa84</t>
+          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04e833dd19df0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9259cc44945602b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4feede92620f22e9</t>
+          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbebd14ac0ed49c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e43910adecb4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2756336b0144995b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c68f32e47611a1</t>
+          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd8d2e3100ea907</t>
+          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e69471258c9ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba35650e2da9649</t>
+          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb9c24b4a27b99e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c08abb8a8067dabe</t>
+          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5c390fe780fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10e7c9ecd47ff09</t>
+          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9393aab76aef47</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de5598243142a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4f92e0b5a77250</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b5097fd06a5b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dbcec9a2251bc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1abb06a257adfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccd80ac908db0d1</t>
+          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09da3c6a02110e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b81878d33b2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2fc82662d2d577e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f11a2204aeac9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4bd4f9915f719</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d99d8a28b97414</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e41db969f64f04</t>
+          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e92b6c49d12909</t>
+          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5fe900bb21047</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6e55b5d347e590</t>
+          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4055b440fbf4926</t>
+          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d661b2249c160667</t>
+          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7fb86315501bea</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48351a9424c5adaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=449ffea81d7dabee</t>
+          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Enginnering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b4c29a1cbe80d1</t>
+          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed68905fe7cf4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Managing Solution Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0cd86430f84239c</t>
+          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Solutions Architect - Airflow (East Coast)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Philadelphia, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34888fd616464280</t>
+          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Baer Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e751aa96956741b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Enginnering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Build-A-Bear Workshop</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, SQL Server, PostgreSQL, Cassandra, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141b4548c3e837f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reno, NV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2640726ebc83e1eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Managing Solution Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99663228cfbf0951</t>
+          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (East Coast)</t>
+          <t>Technical Solutions Engineer - Pre</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Verily</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74680d3dc9bafe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineering - Architecture (Snowflake) BI Consultant</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Baer Group</t>
+          <t>Batchelor &amp; Kimball</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Conyers, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c52c5d83c6a50fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Build-A-Bear Workshop</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,77 +3356,77 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e0d6b0fa569854</t>
+          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Big Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Echo Global Logistics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reno, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0626708bd8ee16</t>
+          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Glue, IAM, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669c1fb330a3b757</t>
+          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technical Solutions Engineer - Pre</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Verily</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7071bed5dd02b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Batchelor &amp; Kimball</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Conyers, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kimball, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1aa0d9278ba8fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d957259a91025ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Big Data Architect</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7429468ddade56be</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9620442cd266fbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>AI DevOps Engineer (Global)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hopkinton, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, ETL, ELT, Power BI, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d564a48f723ff138</t>
+          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Onsite_Azure Data Engineer _Chicago, IL</t>
+          <t>AI Software Engineer - Regrello</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,42 +3671,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37a2ee36d7cc270</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer II - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1b6ba41a8a56f2</t>
+          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d95cae4e2d404f</t>
+          <t>https://www.indeed.com/viewjob?jk=91144e00c41e59f6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer, Data Foundations</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lambda, Scala, Kafka, Oracle, MySQL, MongoDB, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c221ea0da8a688bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer (Global)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3807,11 +3807,11 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,59 +3821,59 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eac67db313991b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Regrello</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c7a2ebafd009</t>
+          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>Cloud Solution Architect (Remote)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58aaf39fa0b76436</t>
+          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Foundations</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Scala, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913f49306655da8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Junior Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Clarity Innovations, LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e557799b2576af0</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Automation Engineer - Senior</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EvergreenHealth</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c55b1cfe2c90261</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Universal City, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,42 +4021,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d59725cfe157aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect (Remote)</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, GCP, Scala, Snowflake</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80add1c41e0267a1</t>
+          <t>https://www.indeed.com/viewjob?jk=229b2a31ef020c77</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Wellvana Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,102 +4101,102 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b05fe1f7203164</t>
+          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Junior Platform Engineer</t>
+          <t>Data Engineer - Finance Technology Solutions</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Clarity Innovations, LLC</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10ffa9f861947b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Automation Engineer - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EvergreenHealth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, SQL Server, REST API integration, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4186b82f48b3e1</t>
+          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Universal City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6537fbdf744212f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Wellvana Health</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99417876eae24963</t>
+          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance Technology Solutions</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573f480e3a91503b</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3338bda845b857ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Sr Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Cassandra, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cdb1faed561dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II - Python, ETL, AWS, Kubernetes</t>
+          <t>Software Engineer/Full Stack Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Databricks, Scala, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d743bfeeb8fa203</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf986da2977e0aa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JSSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee248da0e115e2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>IT Data Scientist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f90da901c6ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Backend Software Engineer (API-focused)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Off Duty Management</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb4473110232100</t>
+          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>COE QE DevOps role - C1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba2d09365f6ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfc96f041f6b858</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer/Full Stack Developer</t>
+          <t>Project Controls, Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MongoDB, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf986da2977e0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Software Engineer II - SRE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JSSA</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff471a82f0fd616b</t>
+          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IT Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac351039409cb17</t>
+          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (API-focused)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Off Duty Management</t>
+          <t>Defense Unicorns</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=251cca66de6f3b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>COE QE DevOps role - C1</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,15 +4713,15 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=046b8c112407479b</t>
+          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Senior Grafana Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,59 +4766,59 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f66e61d041240a</t>
+          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Project Controls, Database Administrator (DBA)</t>
+          <t>Red Hat OpenShift Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8062c19c4d1d41</t>
+          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer II - SRE</t>
+          <t>Senior Full Stack Java Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Softpath System LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Power BI, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed2932ed5336a95</t>
+          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>Enterprise Knowledge</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdace3d6595cd399</t>
+          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Workday Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Defense Unicorns</t>
+          <t>College Board</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb06467c9c6ec61</t>
+          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>Sr. System Administrator</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383f30b24c7b48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Grafana Engineer</t>
+          <t>AI Software Engineer Intern- Bastazo</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Scala, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03542dca349b173</t>
+          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Red Hat OpenShift Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aberdeen Proving Ground, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe00c00e240051b6</t>
+          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Architect</t>
+          <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Softpath System LLC</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Winterville, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, NoSQL, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Step Functions, RDS, Kafka, Tableau, Tableau Server, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5045,216 +5045,6 @@
         </is>
       </c>
       <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64c763f434149f33</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Enterprise Knowledge</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f31219c1b20278a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Workday Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>College Board</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a180802b9be9366</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Sr. System Administrator</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Stellar Solutions</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Terraform, AWS CloudFormation, Docker</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61836c41197600ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Dynamo Technologies</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=522e7d02e7987862</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>AI Software Engineer Intern- Bastazo</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3da3d0ba53df0f86</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Tableau &amp; Alteryx Administrator (Cloud + DevOps Expertise)</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Winterville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, Step Functions, RDS, Kafka, Tableau, Tableau Server, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=653b8eca70818820</t>
         </is>
